--- a/reports/jobs_2026-09-09.xlsx
+++ b/reports/jobs_2026-09-09.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Developer- WD</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -538,7 +538,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -546,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1903,12 +1907,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Full Stack Developer- WD</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1924,7 +1928,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/London/Snowflake-Data-Engineer_SR-45644</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1946,12 +1950,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Python Backend Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1967,7 +1971,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/Data-Engineer-Business-Intelligence-Senior-Consultant-Architect-6_SR-43710-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/London/Snowflake-Data-Engineer_SR-45644</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1989,12 +1993,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Python Backend Engineer</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2010,7 +2014,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/Data-Engineer-Business-Intelligence-Senior-Consultant-Architect-6_SR-43710-1</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2027,17 +2031,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>SharePoint Full Stack role</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2045,7 +2049,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, in</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -2053,12 +2061,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2070,17 +2078,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2088,11 +2096,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, in</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -2100,12 +2104,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2117,17 +2121,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2143,12 +2147,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2165,12 +2169,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2186,7 +2190,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2203,17 +2207,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2221,7 +2225,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -2229,12 +2237,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2251,7 +2259,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2276,7 +2284,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2293,17 +2301,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2313,7 +2321,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2323,12 +2331,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2340,12 +2348,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2360,7 +2368,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2370,12 +2378,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2392,12 +2400,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2417,7 +2425,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2439,12 +2447,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2454,7 +2462,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2464,7 +2472,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2481,12 +2489,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2501,7 +2509,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2511,12 +2519,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2528,17 +2536,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2546,11 +2554,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -2558,12 +2562,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2575,17 +2579,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2601,12 +2605,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2618,17 +2622,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2644,12 +2648,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2661,12 +2665,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2679,7 +2683,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -2687,12 +2695,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2704,17 +2712,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2730,12 +2738,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2747,27 +2755,27 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>SRE Operations Engineer</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2777,12 +2785,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2794,17 +2802,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2820,12 +2828,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2837,27 +2845,27 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>SRE Operations Engineer</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2867,12 +2875,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2884,12 +2892,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2902,7 +2910,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -2910,12 +2922,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2932,7 +2944,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2942,12 +2954,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2957,7 +2969,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2979,7 +2991,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3004,7 +3016,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3026,7 +3038,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3036,12 +3048,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3051,7 +3063,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3073,7 +3085,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3088,7 +3100,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3098,7 +3110,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3115,17 +3127,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3133,11 +3145,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3145,12 +3153,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3162,17 +3170,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3182,7 +3190,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3192,12 +3200,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3209,12 +3217,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3227,7 +3235,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3235,12 +3247,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3257,7 +3269,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3282,7 +3294,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3299,17 +3311,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3317,11 +3329,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3329,12 +3337,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3346,17 +3354,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3366,7 +3374,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3376,12 +3384,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3393,12 +3401,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3411,7 +3419,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3419,12 +3431,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3436,12 +3448,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3456,7 +3468,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3466,12 +3478,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3488,7 +3500,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3513,7 +3525,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3535,7 +3547,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3550,7 +3562,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3560,7 +3572,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3582,7 +3594,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3607,7 +3619,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3624,17 +3636,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Product Operations &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3644,7 +3656,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3654,12 +3666,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3671,17 +3683,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3691,7 +3703,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3701,12 +3713,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3718,17 +3730,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Product Operations &amp; Analytics Intern</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3736,11 +3748,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3748,12 +3756,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3765,17 +3773,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3783,11 +3791,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3795,12 +3799,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3817,7 +3821,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Creative Producer - AI</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -3860,12 +3864,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3881,7 +3885,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -3898,17 +3902,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Creative Producer - AI</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3916,7 +3920,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3924,12 +3932,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3941,17 +3949,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3959,7 +3967,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -3967,12 +3979,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3984,17 +3996,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4004,7 +4016,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>CO-Colombia-Remote</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -4014,12 +4026,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4031,17 +4043,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4049,11 +4061,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -4061,12 +4069,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4078,17 +4086,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4098,7 +4106,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -4108,12 +4116,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4125,17 +4133,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4143,7 +4151,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -4151,12 +4163,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4168,17 +4180,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4188,7 +4200,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4198,12 +4210,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4212,102 +4224,8 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I84"/>
+  <autoFilter ref="A1:I82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4390,8 +4308,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4403,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4471,15 +4387,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Plivo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.plivo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.plivo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4488,18 +4424,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4508,18 +4444,38 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CRED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://careers.cred.club/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://careers.cred.club/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4528,18 +4484,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4548,18 +4504,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4568,18 +4524,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4588,18 +4544,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4608,38 +4564,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PharmEasy</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://pharmeasy.in/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pharmeasy.in/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4648,18 +4584,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4668,18 +4604,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4688,18 +4624,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
